--- a/exports/MARUTI_full_report.xlsx
+++ b/exports/MARUTI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>5.15</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44616.38541666666</v>
+        <v>44616.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>8395.6</v>
+        <v>8195</v>
       </c>
       <c r="I2" t="n">
         <v>8301.644610533525</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>3.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>3.43</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.82</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44634.55208333334</v>
+        <v>44635.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>7298.6</v>
+        <v>7499.8</v>
       </c>
       <c r="I3" t="n">
         <v>7326.463096094202</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>10.94</v>
+        <v>8.48</v>
       </c>
       <c r="L3" t="n">
         <v>3.31</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44664.38541666666</v>
+        <v>44664.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>7505.35</v>
+        <v>7445</v>
       </c>
       <c r="I4" t="n">
         <v>7492.323712374493</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.73</v>
       </c>
       <c r="L4" t="n">
         <v>2.4</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>5.56</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44672.38541666666</v>
+        <v>44672.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>7810.05</v>
+        <v>7865</v>
       </c>
       <c r="I5" t="n">
         <v>7854.224752321548</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.9</v>
+        <v>-5.64</v>
       </c>
       <c r="L5" t="n">
-        <v>5.28</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="n">
         <v>1.7</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>6.09</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>7628.5</v>
+        <v>7409.95</v>
       </c>
       <c r="I6" t="n">
         <v>7471.424580869648</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.01</v>
+        <v>-5.79</v>
       </c>
       <c r="L6" t="n">
-        <v>4.09</v>
+        <v>6.45</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>7.95</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44701.55208333334</v>
+        <v>44704.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>7600</v>
+        <v>7930</v>
       </c>
       <c r="I7" t="n">
         <v>7643.091480672273</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.56</v>
+        <v>-7.02</v>
       </c>
       <c r="L7" t="n">
-        <v>3.22</v>
+        <v>7.35</v>
       </c>
       <c r="M7" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="N7" t="n">
         <v>3.83</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.06</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>8560</v>
+        <v>8510.950000000001</v>
       </c>
       <c r="I8" t="n">
         <v>8547.044987262314</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>64</v>
+        <v>64.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>7.94</v>
+        <v>7.33</v>
       </c>
       <c r="L8" t="n">
         <v>4.73</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>4.31</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>8766</v>
+        <v>8988.35</v>
       </c>
       <c r="I9" t="n">
         <v>8877.563860971477</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-3</v>
+        <v>-5.61</v>
       </c>
       <c r="L9" t="n">
-        <v>5.08</v>
+        <v>6.69</v>
       </c>
       <c r="M9" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="N9" t="n">
-        <v>1.63</v>
+        <v>2.61</v>
       </c>
       <c r="O9" t="n">
         <v>-1.15</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>5.25</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>8696.950000000001</v>
+        <v>8644.700000000001</v>
       </c>
       <c r="I10" t="n">
         <v>8684.881380046147</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.24</v>
+        <v>-3.82</v>
       </c>
       <c r="L10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="M10" t="n">
         <v>0.23</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>4.54</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44802.55208333334</v>
+        <v>44803.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>8835</v>
+        <v>9121.65</v>
       </c>
       <c r="I11" t="n">
         <v>9034.93077801561</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2</v>
+        <v>-5.52</v>
       </c>
       <c r="L11" t="n">
-        <v>2.49</v>
+        <v>5.83</v>
       </c>
       <c r="M11" t="n">
         <v>0.72</v>
       </c>
       <c r="N11" t="n">
-        <v>1.23</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
         <v>-1.2</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.85</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44830.38541666666</v>
+        <v>44830.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>8934.25</v>
+        <v>8801</v>
       </c>
       <c r="I12" t="n">
         <v>8920.466424825881</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.05</v>
+        <v>-3.52</v>
       </c>
       <c r="L12" t="n">
         <v>4.29</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.46</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44859.38541666666</v>
+        <v>44859.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>8929.9</v>
+        <v>9010.1</v>
       </c>
       <c r="I13" t="n">
         <v>8993.275161897</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.46</v>
+        <v>-2.38</v>
       </c>
       <c r="L13" t="n">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
         <v>1.52</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>4.1</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>9230.15</v>
+        <v>9093.549999999999</v>
       </c>
       <c r="I14" t="n">
         <v>9129.903059617263</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>2.44</v>
+        <v>0.93</v>
       </c>
       <c r="L14" t="n">
         <v>1.2</v>
       </c>
       <c r="M14" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="N14" t="n">
         <v>2.26</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.21</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44938.55208333334</v>
+        <v>44939.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>8365</v>
+        <v>8486.35</v>
       </c>
       <c r="I15" t="n">
         <v>8477.29361581999</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K15" t="n">
-        <v>8.01</v>
+        <v>6.68</v>
       </c>
       <c r="L15" t="n">
         <v>1.74</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>3.89</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44987.38541666666</v>
+        <v>44987.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>8600.450000000001</v>
+        <v>8536</v>
       </c>
       <c r="I16" t="n">
         <v>8584.496629641344</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K16" t="n">
-        <v>1.34</v>
+        <v>0.59</v>
       </c>
       <c r="L16" t="n">
         <v>1.7</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>3.72</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>8302</v>
+        <v>8501.549999999999</v>
       </c>
       <c r="I17" t="n">
         <v>8501.190369710017</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>29</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>2.74</v>
+        <v>0.4</v>
       </c>
       <c r="L17" t="n">
         <v>2.35</v>
@@ -1410,7 +1613,7 @@
         <v>1.59</v>
       </c>
       <c r="N17" t="n">
-        <v>1.16</v>
+        <v>2.48</v>
       </c>
       <c r="O17" t="n">
         <v>-2.5</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.09</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45037.55208333334</v>
+        <v>45040.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>8566.049999999999</v>
+        <v>8465.799999999999</v>
       </c>
       <c r="I18" t="n">
         <v>8484.214588196417</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>0.76</v>
+        <v>-0.42</v>
       </c>
       <c r="L18" t="n">
         <v>1.46</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>3.51</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>8606</v>
+        <v>8757.700000000001</v>
       </c>
       <c r="I19" t="n">
         <v>8695.888601934308</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.66</v>
+        <v>-3.45</v>
       </c>
       <c r="L19" t="n">
-        <v>1.73</v>
+        <v>3.74</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.82</v>
+        <v>1.85</v>
       </c>
       <c r="O19" t="n">
         <v>-1.1</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>3.7</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45097.55208333334</v>
+        <v>45098.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>9515.049999999999</v>
+        <v>9446.35</v>
       </c>
       <c r="I20" t="n">
         <v>9451.667968409087</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K20" t="n">
-        <v>8.65</v>
+        <v>7.86</v>
       </c>
       <c r="L20" t="n">
         <v>1.73</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>3.18</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>9530.1</v>
+        <v>9751.5</v>
       </c>
       <c r="I21" t="n">
         <v>9590.684563228166</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.89</v>
+        <v>-3.23</v>
       </c>
       <c r="L21" t="n">
-        <v>1.36</v>
+        <v>3.93</v>
       </c>
       <c r="M21" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="N21" t="n">
-        <v>1.55</v>
+        <v>2.61</v>
       </c>
       <c r="O21" t="n">
         <v>-0.9399999999999999</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>4.05</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45141.38541666666</v>
+        <v>45141.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>9582</v>
+        <v>9520</v>
       </c>
       <c r="I22" t="n">
         <v>9543.536177555281</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.74</v>
+        <v>-2.37</v>
       </c>
       <c r="L22" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="M22" t="n">
         <v>0.75</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>4.36</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45161.38541666666</v>
+        <v>45161.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>9544.700000000001</v>
+        <v>9595</v>
       </c>
       <c r="I23" t="n">
         <v>9568.896197840577</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.26</v>
+        <v>-0.79</v>
       </c>
       <c r="L23" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
         <v>0.46</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>2.62</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>10342.1</v>
+        <v>10223.85</v>
       </c>
       <c r="I24" t="n">
         <v>10266.53544775041</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>7.79</v>
+        <v>6.55</v>
       </c>
       <c r="L24" t="n">
         <v>1.15</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>3.44</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45191.55208333334</v>
+        <v>45194.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>10552.6</v>
+        <v>10621</v>
       </c>
       <c r="I25" t="n">
         <v>10562.19883995786</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.22</v>
+        <v>-3.88</v>
       </c>
       <c r="L25" t="n">
-        <v>3.35</v>
+        <v>4.85</v>
       </c>
       <c r="M25" t="n">
         <v>0.95</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>3.35</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45202.38541666666</v>
+        <v>45202.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>10381.15</v>
+        <v>10325.05</v>
       </c>
       <c r="I26" t="n">
         <v>10336.66606607062</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.26</v>
+        <v>-2.79</v>
       </c>
       <c r="L26" t="n">
         <v>2.99</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>4.4</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45210.55208333334</v>
+        <v>45211.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>10408.25</v>
+        <v>10551.7</v>
       </c>
       <c r="I27" t="n">
         <v>10543.23080938323</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.11</v>
+        <v>2.9</v>
       </c>
       <c r="M27" t="n">
         <v>0.63</v>
       </c>
       <c r="N27" t="n">
-        <v>1.21</v>
+        <v>1.79</v>
       </c>
       <c r="O27" t="n">
         <v>-2.47</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>3.58</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45224.55208333334</v>
+        <v>45225.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>10620</v>
+        <v>10472.35</v>
       </c>
       <c r="I28" t="n">
         <v>10475.17202201988</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>0.65</v>
+        <v>-0.75</v>
       </c>
       <c r="L28" t="n">
         <v>1.25</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="N28" t="n">
-        <v>1.2</v>
+        <v>2.07</v>
       </c>
       <c r="O28" t="n">
         <v>1.79</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>3.63</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45260.38541666666</v>
+        <v>45260.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>10552</v>
+        <v>10635</v>
       </c>
       <c r="I29" t="n">
         <v>10606.75769932992</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.76</v>
+        <v>-1.55</v>
       </c>
       <c r="L29" t="n">
         <v>3.56</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>2.71</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45272.38541666666</v>
+        <v>45272.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>10449.2</v>
+        <v>10350</v>
       </c>
       <c r="I30" t="n">
         <v>10406.05809495272</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.75</v>
+        <v>-2.68</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>3.14</v>
       </c>
       <c r="M30" t="n">
         <v>0.25</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45322.38541666666</v>
+        <v>45322.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>10134.25</v>
+        <v>10161.05</v>
       </c>
       <c r="I31" t="n">
         <v>10151.73915944021</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>49.83333333333334</v>
+        <v>50</v>
       </c>
       <c r="K31" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="L31" t="n">
         <v>1.4</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.02</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45350.38541666666</v>
+        <v>45350.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>11225.4</v>
+        <v>11161.9</v>
       </c>
       <c r="I32" t="n">
         <v>11191.6312574236</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K32" t="n">
-        <v>10.47</v>
+        <v>9.85</v>
       </c>
       <c r="L32" t="n">
         <v>1.04</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>4.24</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45355.55208333334</v>
+        <v>45356.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>11597</v>
+        <v>11700</v>
       </c>
       <c r="I33" t="n">
         <v>11635.33837849619</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.9</v>
+        <v>-4.82</v>
       </c>
       <c r="L33" t="n">
-        <v>4.62</v>
+        <v>5.09</v>
       </c>
       <c r="M33" t="n">
         <v>0.67</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>4.35</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45394.38541666666</v>
+        <v>45394.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>12394</v>
+        <v>12269</v>
       </c>
       <c r="I34" t="n">
         <v>12371.25209981761</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K34" t="n">
-        <v>5.93</v>
+        <v>4.86</v>
       </c>
       <c r="L34" t="n">
         <v>3.7</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>5.37</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45404.55208333334</v>
+        <v>45405.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>12798.95</v>
+        <v>12905.25</v>
       </c>
       <c r="I35" t="n">
         <v>12862.0628648287</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.32</v>
+        <v>-5.19</v>
       </c>
       <c r="L35" t="n">
-        <v>4.97</v>
+        <v>5.3</v>
       </c>
       <c r="M35" t="n">
         <v>0.73</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>5.32</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>12455</v>
+        <v>12300.1</v>
       </c>
       <c r="I36" t="n">
         <v>12399.71981042559</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.49</v>
+        <v>-4.69</v>
       </c>
       <c r="L36" t="n">
-        <v>4.13</v>
+        <v>5.16</v>
       </c>
       <c r="M36" t="n">
         <v>0.39</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>5.57</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45435.55208333334</v>
+        <v>45436.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>12890</v>
+        <v>13001.3</v>
       </c>
       <c r="I37" t="n">
         <v>12922.64357327663</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.8</v>
+        <v>-5.7</v>
       </c>
       <c r="L37" t="n">
-        <v>5.49</v>
+        <v>5.97</v>
       </c>
       <c r="M37" t="n">
         <v>0.67</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>5.01</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45443.38541666666</v>
+        <v>45443.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>12475.85</v>
+        <v>12425</v>
       </c>
       <c r="I38" t="n">
         <v>12471.38918715435</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.04</v>
+        <v>-4.43</v>
       </c>
       <c r="L38" t="n">
-        <v>4.36</v>
+        <v>5.16</v>
       </c>
       <c r="M38" t="n">
         <v>0.46</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>3.71</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45454.38541666666</v>
+        <v>45454.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>12856.55</v>
+        <v>12870</v>
       </c>
       <c r="I39" t="n">
         <v>12857.27004874214</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.47</v>
+        <v>-3.58</v>
       </c>
       <c r="L39" t="n">
-        <v>3.98</v>
+        <v>4.14</v>
       </c>
       <c r="M39" t="n">
         <v>3.22</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>4.81</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45462.38541666666</v>
+        <v>45462.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>12380.05</v>
+        <v>12234</v>
       </c>
       <c r="I40" t="n">
         <v>12367.0636260838</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.81</v>
+        <v>-4.94</v>
       </c>
       <c r="L40" t="n">
-        <v>4.02</v>
+        <v>5.21</v>
       </c>
       <c r="M40" t="n">
         <v>0.07000000000000001</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>4.86</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45481.55208333334</v>
+        <v>45482.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>12045</v>
+        <v>12854.8</v>
       </c>
       <c r="I41" t="n">
         <v>12399.83381662792</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>1.54</v>
+        <v>-5.07</v>
       </c>
       <c r="L41" t="n">
-        <v>1.28</v>
+        <v>5.13</v>
       </c>
       <c r="M41" t="n">
-        <v>0.71</v>
+        <v>2.32</v>
       </c>
       <c r="N41" t="n">
-        <v>0.87</v>
+        <v>6.33</v>
       </c>
       <c r="O41" t="n">
         <v>-2.7</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>6.82</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>12697.1</v>
+        <v>12186.45</v>
       </c>
       <c r="I42" t="n">
         <v>12696.98920403342</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.23</v>
+        <v>-5.2</v>
       </c>
       <c r="L42" t="n">
-        <v>4.6</v>
+        <v>6.43</v>
       </c>
       <c r="M42" t="n">
         <v>1.63</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>7.93</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45554.55208333334</v>
+        <v>45555.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>12329.05</v>
+        <v>12688</v>
       </c>
       <c r="I43" t="n">
         <v>12497.11143345462</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.17</v>
+        <v>-4.12</v>
       </c>
       <c r="L43" t="n">
-        <v>3.15</v>
+        <v>4.26</v>
       </c>
       <c r="M43" t="n">
         <v>1.88</v>
       </c>
       <c r="N43" t="n">
-        <v>1.86</v>
+        <v>2.21</v>
       </c>
       <c r="O43" t="n">
         <v>-3.78</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>4.64</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>13148</v>
+        <v>12815.1</v>
       </c>
       <c r="I44" t="n">
         <v>12903.86277336813</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K44" t="n">
-        <v>3.63</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>2.58</v>
       </c>
       <c r="M44" t="n">
-        <v>0.84</v>
+        <v>1.57</v>
       </c>
       <c r="N44" t="n">
-        <v>1.56</v>
+        <v>3.43</v>
       </c>
       <c r="O44" t="n">
         <v>2.21</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45658.38541666666</v>
+        <v>45658.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>10862.45</v>
+        <v>11185</v>
       </c>
       <c r="I45" t="n">
         <v>11140.35979533717</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>90</v>
+        <v>90.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>15.24</v>
+        <v>12.72</v>
       </c>
       <c r="L45" t="n">
         <v>2.6</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.24</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>12681.2</v>
+        <v>12395.2</v>
       </c>
       <c r="I46" t="n">
         <v>12532.18603513752</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K46" t="n">
-        <v>13.38</v>
+        <v>10.82</v>
       </c>
       <c r="L46" t="n">
         <v>2.94</v>
@@ -3063,7 +3614,7 @@
         <v>1.56</v>
       </c>
       <c r="N46" t="n">
-        <v>1.43</v>
+        <v>2.06</v>
       </c>
       <c r="O46" t="n">
         <v>2.92</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.4</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>11609</v>
+        <v>11914</v>
       </c>
       <c r="I47" t="n">
         <v>11784.17880104225</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K47" t="n">
-        <v>6.34</v>
+        <v>3.88</v>
       </c>
       <c r="L47" t="n">
         <v>2.06</v>
@@ -3120,7 +3683,7 @@
         <v>1.56</v>
       </c>
       <c r="N47" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="O47" t="n">
         <v>-2.06</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.71</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45798.55208333334</v>
+        <v>45799.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>12618</v>
+        <v>12417</v>
       </c>
       <c r="I48" t="n">
         <v>12479.412136454</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K48" t="n">
-        <v>5.91</v>
+        <v>4.22</v>
       </c>
       <c r="L48" t="n">
         <v>5.25</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>4.83</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45814.55208333334</v>
+        <v>45817.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>12463</v>
+        <v>12603</v>
       </c>
       <c r="I49" t="n">
         <v>12525.41884734388</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.37</v>
+        <v>-1.5</v>
       </c>
       <c r="L49" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="M49" t="n">
         <v>0.39</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>4.29</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45838.38541666666</v>
+        <v>45838.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>12426</v>
+        <v>12406</v>
       </c>
       <c r="I50" t="n">
         <v>12416.19944356741</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.4</v>
+        <v>-1.56</v>
       </c>
       <c r="L50" t="n">
         <v>3.39</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>3.13</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45840.55208333334</v>
+        <v>45841.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>12615</v>
+        <v>12805</v>
       </c>
       <c r="I51" t="n">
         <v>12794.14441568904</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.68</v>
+        <v>-3.22</v>
       </c>
       <c r="L51" t="n">
-        <v>1.91</v>
+        <v>3.31</v>
       </c>
       <c r="M51" t="n">
         <v>0.35</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.16</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>12385</v>
+        <v>12333</v>
       </c>
       <c r="I52" t="n">
         <v>12358.5691135818</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.28</v>
+        <v>-3.69</v>
       </c>
       <c r="L52" t="n">
         <v>3.8</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>3.77</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45880.55208333334</v>
+        <v>45881.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>12583</v>
+        <v>12854</v>
       </c>
       <c r="I53" t="n">
         <v>12682.63285217479</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.03</v>
+        <v>-4.22</v>
       </c>
       <c r="L53" t="n">
-        <v>3.62</v>
+        <v>5.08</v>
       </c>
       <c r="M53" t="n">
         <v>0.35</v>
       </c>
       <c r="N53" t="n">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="O53" t="n">
         <v>-0.4</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>4.56</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45961.55208333334</v>
+        <v>45964.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>16155</v>
+        <v>15631</v>
       </c>
       <c r="I54" t="n">
         <v>16010.97874480091</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>80.16666666666667</v>
+        <v>83</v>
       </c>
       <c r="K54" t="n">
-        <v>25.68</v>
+        <v>21.6</v>
       </c>
       <c r="L54" t="n">
         <v>1.93</v>
       </c>
       <c r="M54" t="n">
-        <v>0.32</v>
+        <v>0.86</v>
       </c>
       <c r="N54" t="n">
-        <v>1.88</v>
+        <v>3.23</v>
       </c>
       <c r="O54" t="n">
         <v>2.1</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>5.79</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>15822</v>
+        <v>16114</v>
       </c>
       <c r="I55" t="n">
         <v>15962.94102649458</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.22</v>
+        <v>-3.09</v>
       </c>
       <c r="L55" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="M55" t="n">
         <v>1.05</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>4.29</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>16806</v>
+        <v>16658</v>
       </c>
       <c r="I56" t="n">
         <v>16789.12040049371</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K56" t="n">
-        <v>4.29</v>
+        <v>3.38</v>
       </c>
       <c r="L56" t="n">
         <v>2.34</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>3.97</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46062.55208333334</v>
+        <v>46063.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>14980</v>
+        <v>15221</v>
       </c>
       <c r="I57" t="n">
         <v>15133.97702299039</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K57" t="n">
-        <v>10.07</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L57" t="n">
         <v>0.9</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.6</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>14810</v>
+        <v>14337</v>
       </c>
       <c r="I58" t="n">
         <v>14709.92752079113</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.7</v>
+        <v>-5.81</v>
       </c>
       <c r="L58" t="n">
-        <v>2.74</v>
+        <v>6.66</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6</v>
+        <v>2.72</v>
       </c>
       <c r="N58" t="n">
-        <v>2.57</v>
+        <v>2.98</v>
       </c>
       <c r="O58" t="n">
         <v>1.04</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.4</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>12813</v>
+        <v>13714</v>
       </c>
       <c r="I59" t="n">
         <v>13022.53216861931</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K59" t="n">
-        <v>10.63</v>
+        <v>4.35</v>
       </c>
       <c r="L59" t="n">
         <v>2.42</v>
@@ -3804,7 +4511,7 @@
         <v>5.31</v>
       </c>
       <c r="N59" t="n">
-        <v>2.89</v>
+        <v>5.91</v>
       </c>
       <c r="O59" t="n">
         <v>-2.98</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.4</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>13239</v>
+        <v>13017</v>
       </c>
       <c r="I60" t="n">
         <v>13094.37525982503</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.46</v>
+        <v>-5.08</v>
       </c>
       <c r="L60" t="n">
         <v>6.46</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.01</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>13350</v>
+        <v>13913</v>
       </c>
       <c r="I61" t="n">
         <v>13499.30104466949</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.56</v>
+        <v>-6.88</v>
       </c>
       <c r="L61" t="n">
-        <v>3.77</v>
+        <v>7.25</v>
       </c>
       <c r="M61" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="N61" t="n">
-        <v>1.78</v>
+        <v>3.42</v>
       </c>
       <c r="O61" t="n">
         <v>-1.69</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.39</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46211.55208333334</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>13973</v>
+        <v>13780</v>
       </c>
       <c r="I62" t="n">
         <v>13959.32239658488</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K62" t="n">
-        <v>0.43</v>
+        <v>-0.96</v>
       </c>
       <c r="L62" t="n">
         <v>5.12</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.06</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>13805</v>
+        <v>13905</v>
       </c>
       <c r="I63" t="n">
         <v>13904.76710515437</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.18</v>
+        <v>-0.91</v>
       </c>
       <c r="L63" t="n">
         <v>1.87</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.25</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46253.38541666666</v>
+        <v>46253.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>13708</v>
+        <v>13650</v>
       </c>
       <c r="I64" t="n">
         <v>13672.1879971054</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.42</v>
+        <v>-1.83</v>
       </c>
       <c r="L64" t="n">
         <v>1.99</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>93</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6251,7 +7038,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.6</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="6">
@@ -6261,7 +7048,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="7">
@@ -6271,7 +7058,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="8">
@@ -6281,7 +7068,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -6291,7 +7078,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.6</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="10">
@@ -6301,7 +7088,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -6311,7 +7098,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -6321,7 +7108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6331,7 +7118,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.8</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="14">
@@ -6341,7 +7128,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.33</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="15">
@@ -6351,7 +7138,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.99</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="16">
@@ -6361,7 +7148,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.65</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="17">
@@ -6371,7 +7158,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25.68</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="18">
@@ -6381,7 +7168,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -6391,7 +7178,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.94</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="20">
@@ -6401,7 +7188,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.74</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="21">
@@ -6411,7 +7198,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.46</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="22">
@@ -6421,7 +7208,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -6441,7 +7228,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="25">
@@ -6461,7 +7248,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="27">
@@ -6471,7 +7258,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.7</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="28">
@@ -6481,7 +7268,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
